--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/uk-ua.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/uk-ua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B4B006-4B6B-4004-AD2D-1929582FC06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDAA72F-29D4-48CA-BBE4-E9FA7C3F65AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="264">
   <si>
     <t>Verify if it is published by Yi</t>
   </si>
@@ -863,7 +863,17 @@
 </t>
   </si>
   <si>
-    <t>Not</t>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+</t>
   </si>
 </sst>
 </file>
@@ -4705,22 +4715,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.61328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.69140625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4733,7 +4743,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>256</v>
@@ -4747,7 +4757,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -4757,7 +4767,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4766,7 +4776,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="62.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4797,7 +4807,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="126.9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="126" x14ac:dyDescent="0.45">
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>258</v>
@@ -4811,7 +4821,9 @@
       <c r="F6" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="16"/>
+      <c r="G6" s="16" t="s">
+        <v>262</v>
+      </c>
       <c r="H6" s="14">
         <v>1</v>
       </c>
@@ -4824,7 +4836,7 @@
       <c r="K6" s="14"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="47.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="63" x14ac:dyDescent="0.45">
       <c r="B7" s="14"/>
       <c r="C7" s="42" t="s">
         <v>257</v>
@@ -4838,7 +4850,9 @@
       <c r="F7" s="44" t="s">
         <v>261</v>
       </c>
-      <c r="G7" s="16"/>
+      <c r="G7" s="16" t="s">
+        <v>263</v>
+      </c>
       <c r="H7" s="14">
         <v>1</v>
       </c>
@@ -4851,7 +4865,7 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -4861,7 +4875,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -4870,7 +4884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -4885,7 +4899,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -4900,7 +4914,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8"/>
@@ -4910,14 +4924,14 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4928,7 +4942,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4939,7 +4953,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4950,7 +4964,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4961,7 +4975,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4972,7 +4986,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4983,7 +4997,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4994,7 +5008,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -5005,7 +5019,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -5016,7 +5030,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5027,7 +5041,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -5038,7 +5052,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -5049,7 +5063,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -5060,7 +5074,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -5071,7 +5085,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5082,7 +5096,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -5093,7 +5107,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -5104,7 +5118,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -5115,7 +5129,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -5126,7 +5140,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -5137,7 +5151,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -5196,29 +5210,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R131"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>249</v>
       </c>
@@ -5226,7 +5240,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -5234,7 +5248,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -5242,7 +5256,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -5250,13 +5264,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -5264,7 +5278,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -5279,7 +5293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -5293,7 +5307,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -5307,7 +5321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5321,7 +5335,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5335,7 +5349,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5349,7 +5363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5363,7 +5377,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5377,7 +5391,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5391,7 +5405,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5405,7 +5419,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5419,7 +5433,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5433,7 +5447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5447,7 +5461,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5461,7 +5475,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5475,7 +5489,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5489,7 +5503,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5503,7 +5517,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5517,7 +5531,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5531,7 +5545,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5545,7 +5559,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5559,7 +5573,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5573,7 +5587,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5587,7 +5601,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5601,7 +5615,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5615,7 +5629,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5629,7 +5643,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5643,7 +5657,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5657,7 +5671,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5671,7 +5685,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5685,7 +5699,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5699,7 +5713,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5713,7 +5727,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5727,7 +5741,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5741,7 +5755,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5755,7 +5769,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5769,7 +5783,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5783,7 +5797,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5797,7 +5811,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5811,7 +5825,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5825,7 +5839,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5839,7 +5853,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5853,7 +5867,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5867,7 +5881,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5881,7 +5895,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5895,7 +5909,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5909,7 +5923,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5923,7 +5937,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5937,12 +5951,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -5956,7 +5970,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -5970,7 +5984,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -5984,7 +5998,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -5998,7 +6012,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -6012,7 +6026,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -6026,7 +6040,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -6040,7 +6054,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -6054,7 +6068,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -6068,7 +6082,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -6082,7 +6096,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -6096,7 +6110,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -6110,7 +6124,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -6124,7 +6138,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -6138,7 +6152,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -6152,7 +6166,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -6166,7 +6180,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -6180,7 +6194,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -6194,7 +6208,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -6208,7 +6222,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -6222,7 +6236,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -6236,7 +6250,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -6250,7 +6264,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -6264,7 +6278,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -6278,7 +6292,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -6292,7 +6306,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -6306,7 +6320,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -6320,7 +6334,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -6334,7 +6348,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -6348,7 +6362,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -6362,7 +6376,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -6376,7 +6390,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -6390,7 +6404,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -6404,7 +6418,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -6418,7 +6432,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -6432,7 +6446,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -6446,7 +6460,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -6460,7 +6474,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -6474,7 +6488,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -6488,7 +6502,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -6502,7 +6516,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -6516,7 +6530,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -6530,7 +6544,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -6544,7 +6558,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -6558,7 +6572,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -6572,7 +6586,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -6586,7 +6600,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -6600,7 +6614,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -6614,7 +6628,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -6628,7 +6642,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -6642,7 +6656,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -6656,7 +6670,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -6670,7 +6684,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -6684,7 +6698,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -6698,7 +6712,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -6712,7 +6726,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -6726,7 +6740,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -6740,7 +6754,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -6754,7 +6768,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -6768,7 +6782,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -6782,7 +6796,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -6796,7 +6810,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -6810,7 +6824,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -6824,7 +6838,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -6838,7 +6852,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -6852,7 +6866,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -6866,7 +6880,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -6880,7 +6894,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -6894,7 +6908,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -6908,7 +6922,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -6922,7 +6936,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -6936,7 +6950,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -6950,7 +6964,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -6964,7 +6978,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -7001,29 +7015,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R131"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>250</v>
       </c>
@@ -7031,7 +7045,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -7039,7 +7053,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -7047,7 +7061,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -7055,13 +7069,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -7069,7 +7083,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -7084,7 +7098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -7098,7 +7112,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -7112,7 +7126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -7126,7 +7140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -7140,7 +7154,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -7154,7 +7168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -7168,7 +7182,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -7182,7 +7196,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -7196,7 +7210,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -7210,7 +7224,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -7224,7 +7238,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7238,7 +7252,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7252,7 +7266,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7266,7 +7280,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7280,7 +7294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7294,7 +7308,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7308,7 +7322,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7322,7 +7336,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7336,7 +7350,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7350,7 +7364,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7364,7 +7378,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7378,7 +7392,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7392,7 +7406,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7406,7 +7420,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7420,7 +7434,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7434,7 +7448,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7448,7 +7462,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7462,7 +7476,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7476,7 +7490,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7490,7 +7504,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7504,7 +7518,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7518,7 +7532,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7532,7 +7546,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7546,7 +7560,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7560,7 +7574,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7574,7 +7588,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7588,7 +7602,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7602,7 +7616,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7616,7 +7630,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7630,7 +7644,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7644,7 +7658,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7658,7 +7672,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7672,7 +7686,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7686,7 +7700,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7700,7 +7714,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7714,7 +7728,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7728,7 +7742,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -7742,12 +7756,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -7761,7 +7775,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -7775,7 +7789,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -7789,7 +7803,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -7803,7 +7817,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -7817,7 +7831,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -7831,7 +7845,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -7845,7 +7859,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -7859,7 +7873,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -7873,7 +7887,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -7887,7 +7901,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -7901,7 +7915,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -7915,7 +7929,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -7929,7 +7943,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -7943,7 +7957,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -7957,7 +7971,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -7971,7 +7985,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -7985,7 +7999,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -7999,7 +8013,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -8013,7 +8027,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -8027,7 +8041,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -8041,7 +8055,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -8055,7 +8069,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -8069,7 +8083,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -8083,7 +8097,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -8097,7 +8111,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -8111,7 +8125,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -8125,7 +8139,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -8139,7 +8153,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -8153,7 +8167,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -8167,7 +8181,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -8181,7 +8195,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -8195,7 +8209,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -8209,7 +8223,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -8223,7 +8237,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -8237,7 +8251,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -8251,7 +8265,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -8265,7 +8279,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -8279,7 +8293,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -8293,7 +8307,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -8307,7 +8321,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -8321,7 +8335,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -8335,7 +8349,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -8349,7 +8363,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -8363,7 +8377,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -8377,7 +8391,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -8391,7 +8405,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -8405,7 +8419,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -8419,7 +8433,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -8433,7 +8447,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -8447,7 +8461,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -8461,7 +8475,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -8475,7 +8489,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -8489,7 +8503,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -8503,7 +8517,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -8517,7 +8531,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -8531,7 +8545,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -8545,7 +8559,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -8559,7 +8573,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -8573,7 +8587,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -8587,7 +8601,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -8601,7 +8615,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -8615,7 +8629,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -8629,7 +8643,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -8643,7 +8657,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -8657,7 +8671,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -8671,7 +8685,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -8685,7 +8699,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -8699,7 +8713,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -8713,7 +8727,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -8727,7 +8741,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -8741,7 +8755,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -8755,7 +8769,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -8769,7 +8783,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -8806,29 +8820,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>251</v>
       </c>
@@ -8836,7 +8850,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -8844,7 +8858,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -8852,7 +8866,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -8860,13 +8874,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -8874,7 +8888,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -8889,7 +8903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -8903,7 +8917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -8917,7 +8931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -8931,7 +8945,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -8945,7 +8959,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -8959,7 +8973,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -8973,7 +8987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -8987,7 +9001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9001,7 +9015,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9015,7 +9029,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9029,7 +9043,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9043,7 +9057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9057,7 +9071,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9071,7 +9085,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9085,7 +9099,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9099,7 +9113,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9113,7 +9127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9127,7 +9141,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9141,7 +9155,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9155,7 +9169,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9169,7 +9183,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9183,7 +9197,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9197,7 +9211,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9211,7 +9225,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9225,7 +9239,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9239,7 +9253,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9253,7 +9267,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9267,7 +9281,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9281,7 +9295,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9295,7 +9309,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9309,7 +9323,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9323,7 +9337,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9337,7 +9351,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9351,7 +9365,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9365,7 +9379,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9379,7 +9393,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9393,7 +9407,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9407,7 +9421,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9421,7 +9435,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9435,7 +9449,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9449,7 +9463,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9463,7 +9477,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9477,7 +9491,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9491,7 +9505,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9505,7 +9519,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9519,7 +9533,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9533,12 +9547,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -9552,7 +9566,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -9566,7 +9580,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -9580,7 +9594,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -9594,7 +9608,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -9608,7 +9622,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -9622,7 +9636,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -9636,7 +9650,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -9657,7 +9671,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -9678,7 +9692,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -9699,7 +9713,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -9720,7 +9734,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -9741,7 +9755,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -9762,7 +9776,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -9783,7 +9797,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -9804,7 +9818,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -9825,7 +9839,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -9846,7 +9860,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -9867,7 +9881,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -9888,7 +9902,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -9909,7 +9923,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -9930,7 +9944,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -9951,7 +9965,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -9972,7 +9986,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -9993,7 +10007,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -10014,7 +10028,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -10035,7 +10049,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -10056,7 +10070,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -10077,7 +10091,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -10098,7 +10112,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -10119,7 +10133,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -10140,7 +10154,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -10161,7 +10175,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -10182,7 +10196,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -10203,7 +10217,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -10224,7 +10238,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -10245,7 +10259,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -10266,7 +10280,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -10287,7 +10301,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -10308,7 +10322,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -10329,7 +10343,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -10350,7 +10364,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -10371,7 +10385,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -10392,7 +10406,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -10413,7 +10427,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -10434,7 +10448,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -10455,7 +10469,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -10476,7 +10490,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -10497,7 +10511,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -10518,7 +10532,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -10539,7 +10553,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -10560,7 +10574,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -10581,7 +10595,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -10602,7 +10616,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -10623,7 +10637,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -10644,7 +10658,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -10665,7 +10679,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -10686,7 +10700,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -10707,7 +10721,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -10728,7 +10742,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -10749,7 +10763,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -10770,7 +10784,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -10791,7 +10805,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -10812,7 +10826,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -10833,7 +10847,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -10854,7 +10868,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -10875,7 +10889,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -10896,7 +10910,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -10917,7 +10931,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -10938,7 +10952,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -10959,7 +10973,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -10980,7 +10994,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -11001,7 +11015,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -11022,7 +11036,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -11043,7 +11057,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -11064,7 +11078,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -11108,29 +11122,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>252</v>
       </c>
@@ -11138,7 +11152,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -11146,7 +11160,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -11154,7 +11168,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -11162,13 +11176,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -11176,7 +11190,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -11191,7 +11205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11205,7 +11219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11219,7 +11233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11233,7 +11247,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11247,7 +11261,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11261,7 +11275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11275,7 +11289,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11289,7 +11303,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11303,7 +11317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11317,7 +11331,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11331,7 +11345,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11345,7 +11359,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11359,7 +11373,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11373,7 +11387,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11387,7 +11401,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11401,7 +11415,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11415,7 +11429,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11429,7 +11443,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11443,7 +11457,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11457,7 +11471,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11471,7 +11485,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11485,7 +11499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11499,7 +11513,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11513,7 +11527,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11527,7 +11541,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11541,7 +11555,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11555,7 +11569,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11569,7 +11583,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11583,7 +11597,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11597,7 +11611,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -11611,7 +11625,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -11625,7 +11639,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -11639,7 +11653,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -11653,7 +11667,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -11667,7 +11681,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -11681,7 +11695,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -11695,7 +11709,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -11709,7 +11723,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -11723,7 +11737,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -11737,7 +11751,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -11751,7 +11765,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -11765,7 +11779,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -11779,7 +11793,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -11793,7 +11807,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -11807,7 +11821,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -11821,7 +11835,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -11835,12 +11849,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -11854,7 +11868,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -11868,7 +11882,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -11882,7 +11896,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -11896,7 +11910,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -11910,7 +11924,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -11924,7 +11938,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -11938,7 +11952,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -11959,7 +11973,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -11980,7 +11994,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -12001,7 +12015,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -12022,7 +12036,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -12043,7 +12057,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -12064,7 +12078,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -12085,7 +12099,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -12106,7 +12120,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -12127,7 +12141,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -12148,7 +12162,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -12169,7 +12183,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -12190,7 +12204,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -12211,7 +12225,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -12232,7 +12246,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -12253,7 +12267,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -12274,7 +12288,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -12295,7 +12309,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -12316,7 +12330,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -12337,7 +12351,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -12358,7 +12372,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -12379,7 +12393,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -12400,7 +12414,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -12421,7 +12435,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -12442,7 +12456,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -12463,7 +12477,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -12484,7 +12498,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -12505,7 +12519,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -12526,7 +12540,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -12547,7 +12561,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -12568,7 +12582,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -12589,7 +12603,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -12610,7 +12624,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -12631,7 +12645,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -12652,7 +12666,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -12673,7 +12687,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -12694,7 +12708,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -12715,7 +12729,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -12736,7 +12750,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -12757,7 +12771,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -12778,7 +12792,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -12799,7 +12813,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -12820,7 +12834,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -12841,7 +12855,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -12862,7 +12876,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -12883,7 +12897,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -12904,7 +12918,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -12925,7 +12939,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -12946,7 +12960,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -12967,7 +12981,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -12988,7 +13002,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -13009,7 +13023,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -13030,7 +13044,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -13051,7 +13065,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -13072,7 +13086,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -13093,7 +13107,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -13114,7 +13128,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -13135,7 +13149,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -13156,7 +13170,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -13177,7 +13191,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -13198,7 +13212,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -13219,7 +13233,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -13240,7 +13254,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -13261,7 +13275,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -13282,7 +13296,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -13303,7 +13317,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -13324,7 +13338,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -13345,7 +13359,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -13366,7 +13380,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -13410,29 +13424,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>253</v>
       </c>
@@ -13440,7 +13454,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -13448,7 +13462,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -13456,7 +13470,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -13464,13 +13478,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -13478,7 +13492,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -13493,7 +13507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -13507,7 +13521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -13521,7 +13535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -13535,7 +13549,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -13549,7 +13563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -13563,7 +13577,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -13577,7 +13591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -13591,7 +13605,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -13605,7 +13619,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -13619,7 +13633,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -13633,7 +13647,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -13647,7 +13661,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -13661,7 +13675,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -13675,7 +13689,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -13689,7 +13703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -13703,7 +13717,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -13717,7 +13731,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -13731,7 +13745,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -13745,7 +13759,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -13759,7 +13773,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -13773,7 +13787,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -13787,7 +13801,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -13801,7 +13815,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -13815,7 +13829,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -13829,7 +13843,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -13843,7 +13857,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -13857,7 +13871,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -13871,7 +13885,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -13885,7 +13899,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -13899,7 +13913,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -13913,7 +13927,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -13927,7 +13941,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -13941,7 +13955,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -13955,7 +13969,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -13969,7 +13983,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -13983,7 +13997,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -13997,7 +14011,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14011,7 +14025,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14025,7 +14039,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14039,7 +14053,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14053,7 +14067,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14067,7 +14081,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14081,7 +14095,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14095,7 +14109,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14109,7 +14123,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14123,7 +14137,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14137,12 +14151,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -14156,7 +14170,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -14170,7 +14184,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -14184,7 +14198,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -14198,7 +14212,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -14212,7 +14226,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -14226,7 +14240,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -14240,7 +14254,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -14261,7 +14275,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -14282,7 +14296,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -14303,7 +14317,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -14324,7 +14338,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -14345,7 +14359,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -14366,7 +14380,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -14387,7 +14401,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -14408,7 +14422,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -14429,7 +14443,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -14450,7 +14464,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -14471,7 +14485,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -14492,7 +14506,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -14513,7 +14527,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -14534,7 +14548,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -14555,7 +14569,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -14576,7 +14590,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -14597,7 +14611,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -14618,7 +14632,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -14639,7 +14653,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -14660,7 +14674,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -14681,7 +14695,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -14702,7 +14716,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -14723,7 +14737,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -14744,7 +14758,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -14765,7 +14779,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -14786,7 +14800,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -14807,7 +14821,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -14828,7 +14842,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -14849,7 +14863,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -14870,7 +14884,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -14891,7 +14905,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -14912,7 +14926,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -14933,7 +14947,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -14954,7 +14968,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -14975,7 +14989,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -14996,7 +15010,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -15017,7 +15031,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -15038,7 +15052,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -15059,7 +15073,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -15080,7 +15094,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -15101,7 +15115,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -15122,7 +15136,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -15143,7 +15157,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -15164,7 +15178,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -15185,7 +15199,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -15206,7 +15220,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -15227,7 +15241,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -15248,7 +15262,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -15269,7 +15283,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -15290,7 +15304,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -15311,7 +15325,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -15332,7 +15346,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -15353,7 +15367,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -15374,7 +15388,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -15395,7 +15409,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -15416,7 +15430,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -15437,7 +15451,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -15458,7 +15472,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -15479,7 +15493,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -15500,7 +15514,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -15521,7 +15535,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -15542,7 +15556,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -15563,7 +15577,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -15584,7 +15598,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -15605,7 +15619,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -15626,7 +15640,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -15647,7 +15661,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -15668,7 +15682,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -15712,29 +15726,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>254</v>
       </c>
@@ -15742,7 +15756,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -15750,7 +15764,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -15758,7 +15772,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -15766,13 +15780,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -15780,7 +15794,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -15795,7 +15809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -15809,7 +15823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -15823,7 +15837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -15837,7 +15851,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -15851,7 +15865,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -15865,7 +15879,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -15879,7 +15893,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -15893,7 +15907,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -15907,7 +15921,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -15921,7 +15935,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -15935,7 +15949,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -15949,7 +15963,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -15963,7 +15977,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -15977,7 +15991,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -15991,7 +16005,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16005,7 +16019,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16019,7 +16033,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16033,7 +16047,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16047,7 +16061,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16061,7 +16075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16075,7 +16089,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16089,7 +16103,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16103,7 +16117,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16117,7 +16131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16131,7 +16145,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16145,7 +16159,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16159,7 +16173,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16173,7 +16187,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16187,7 +16201,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16201,7 +16215,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16215,7 +16229,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16229,7 +16243,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16243,7 +16257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16257,7 +16271,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16271,7 +16285,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16285,7 +16299,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16299,7 +16313,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16313,7 +16327,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16327,7 +16341,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16341,7 +16355,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16355,7 +16369,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16369,7 +16383,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16383,7 +16397,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16397,7 +16411,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -16411,7 +16425,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -16425,7 +16439,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -16439,12 +16453,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -16458,7 +16472,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -16472,7 +16486,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -16486,7 +16500,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -16500,7 +16514,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -16514,7 +16528,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -16528,7 +16542,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -16542,7 +16556,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -16563,7 +16577,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -16584,7 +16598,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -16605,7 +16619,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -16626,7 +16640,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -16647,7 +16661,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -16668,7 +16682,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -16689,7 +16703,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -16710,7 +16724,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -16731,7 +16745,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -16752,7 +16766,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -16773,7 +16787,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -16794,7 +16808,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -16815,7 +16829,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -16836,7 +16850,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -16857,7 +16871,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -16878,7 +16892,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -16899,7 +16913,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -16920,7 +16934,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -16941,7 +16955,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -16962,7 +16976,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -16983,7 +16997,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -17004,7 +17018,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -17025,7 +17039,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -17046,7 +17060,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -17067,7 +17081,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -17088,7 +17102,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -17109,7 +17123,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -17130,7 +17144,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -17151,7 +17165,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -17172,7 +17186,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -17193,7 +17207,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -17214,7 +17228,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -17235,7 +17249,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -17256,7 +17270,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -17277,7 +17291,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -17298,7 +17312,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -17319,7 +17333,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -17340,7 +17354,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -17361,7 +17375,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -17382,7 +17396,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -17403,7 +17417,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -17424,7 +17438,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -17445,7 +17459,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -17466,7 +17480,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -17487,7 +17501,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -17508,7 +17522,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -17529,7 +17543,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -17550,7 +17564,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -17571,7 +17585,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -17592,7 +17606,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -17613,7 +17627,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -17634,7 +17648,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -17655,7 +17669,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -17676,7 +17690,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -17697,7 +17711,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -17718,7 +17732,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -17739,7 +17753,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -17760,7 +17774,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -17781,7 +17795,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -17802,7 +17816,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -17823,7 +17837,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -17844,7 +17858,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -17865,7 +17879,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -17886,7 +17900,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -17907,7 +17921,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -17928,7 +17942,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -17949,7 +17963,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -17970,7 +17984,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -18014,29 +18028,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>255</v>
       </c>
@@ -18044,7 +18058,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -18052,7 +18066,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -18060,7 +18074,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -18068,13 +18082,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -18082,7 +18096,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -18097,7 +18111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -18111,7 +18125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -18125,7 +18139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -18139,7 +18153,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -18153,7 +18167,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -18167,7 +18181,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -18181,7 +18195,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -18195,7 +18209,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -18209,7 +18223,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -18223,7 +18237,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -18237,7 +18251,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -18251,7 +18265,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -18265,7 +18279,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -18279,7 +18293,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -18293,7 +18307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -18307,7 +18321,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -18321,7 +18335,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -18335,7 +18349,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -18349,7 +18363,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -18363,7 +18377,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -18377,7 +18391,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -18391,7 +18405,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -18405,7 +18419,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -18419,7 +18433,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -18433,7 +18447,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -18447,7 +18461,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -18461,7 +18475,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -18475,7 +18489,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -18489,7 +18503,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -18503,7 +18517,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -18517,7 +18531,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -18531,7 +18545,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -18545,7 +18559,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -18559,7 +18573,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -18573,7 +18587,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -18587,7 +18601,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -18601,7 +18615,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -18615,7 +18629,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -18629,7 +18643,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -18643,7 +18657,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -18657,7 +18671,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -18671,7 +18685,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -18685,7 +18699,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -18699,7 +18713,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -18713,7 +18727,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -18727,7 +18741,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -18741,12 +18755,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -18760,7 +18774,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -18774,7 +18788,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -18788,7 +18802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -18802,7 +18816,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -18816,7 +18830,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -18830,7 +18844,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -18844,7 +18858,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -18865,7 +18879,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -18886,7 +18900,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -18907,7 +18921,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -18928,7 +18942,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -18949,7 +18963,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -18970,7 +18984,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -18991,7 +19005,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -19012,7 +19026,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -19033,7 +19047,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -19054,7 +19068,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -19075,7 +19089,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -19096,7 +19110,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -19117,7 +19131,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -19138,7 +19152,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -19159,7 +19173,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -19180,7 +19194,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -19201,7 +19215,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -19222,7 +19236,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -19243,7 +19257,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -19264,7 +19278,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -19285,7 +19299,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -19306,7 +19320,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -19327,7 +19341,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -19348,7 +19362,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -19369,7 +19383,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -19390,7 +19404,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -19411,7 +19425,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -19432,7 +19446,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -19453,7 +19467,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -19474,7 +19488,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -19495,7 +19509,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -19516,7 +19530,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -19537,7 +19551,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -19558,7 +19572,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -19579,7 +19593,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -19600,7 +19614,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -19621,7 +19635,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -19642,7 +19656,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -19663,7 +19677,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -19684,7 +19698,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -19705,7 +19719,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -19726,7 +19740,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -19747,7 +19761,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -19768,7 +19782,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -19789,7 +19803,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -19810,7 +19824,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -19831,7 +19845,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -19852,7 +19866,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -19873,7 +19887,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -19894,7 +19908,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -19915,7 +19929,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -19936,7 +19950,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -19957,7 +19971,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -19978,7 +19992,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -19999,7 +20013,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -20020,7 +20034,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -20041,7 +20055,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -20062,7 +20076,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -20083,7 +20097,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -20104,7 +20118,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -20125,7 +20139,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -20146,7 +20160,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -20167,7 +20181,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -20188,7 +20202,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -20209,7 +20223,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -20230,7 +20244,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -20251,7 +20265,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -20272,7 +20286,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">

--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/uk-ua.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/uk-ua.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDAA72F-29D4-48CA-BBE4-E9FA7C3F65AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4BDAA72F-29D4-48CA-BBE4-E9FA7C3F65AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD07BB5-2066-4413-9509-6D138DCAD0CE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4715,22 +4715,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.69140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.61328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.69140625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4743,7 +4743,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>256</v>
@@ -4757,7 +4757,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -4767,7 +4767,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4776,7 +4776,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="62.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="126" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="126.9" x14ac:dyDescent="0.4">
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>258</v>
@@ -4836,7 +4836,7 @@
       <c r="K6" s="14"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="63" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="63.45" x14ac:dyDescent="0.4">
       <c r="B7" s="14"/>
       <c r="C7" s="42" t="s">
         <v>257</v>
@@ -4865,17 +4865,13 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" s="15" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8"/>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -4884,7 +4880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -4892,14 +4888,8 @@
       <c r="D10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="11" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -4907,14 +4897,8 @@
       <c r="D11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8"/>
@@ -4924,14 +4908,14 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4942,7 +4926,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4953,7 +4937,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4964,7 +4948,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4975,7 +4959,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4986,7 +4970,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4997,7 +4981,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -5008,7 +4992,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -5019,7 +5003,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -5030,7 +5014,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5041,7 +5025,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -5052,7 +5036,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -5063,7 +5047,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -5074,7 +5058,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -5085,7 +5069,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5096,7 +5080,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -5107,7 +5091,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -5118,7 +5102,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -5129,7 +5113,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -5140,7 +5124,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -5151,7 +5135,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -5165,7 +5149,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F8:I1048576 F1:I1 H2:J5">
+  <conditionalFormatting sqref="F12:I1048576 F1:I1 H2:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -5184,7 +5168,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5210,29 +5194,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R131"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>249</v>
       </c>
@@ -5240,7 +5224,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -5248,7 +5232,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -5256,7 +5240,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -5264,13 +5248,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -5278,7 +5262,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -5293,7 +5277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -5307,7 +5291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -5321,7 +5305,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5335,7 +5319,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5349,7 +5333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5363,7 +5347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5377,7 +5361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5391,7 +5375,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5405,7 +5389,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5419,7 +5403,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5433,7 +5417,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5447,7 +5431,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5461,7 +5445,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5475,7 +5459,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5489,7 +5473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5503,7 +5487,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5517,7 +5501,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5531,7 +5515,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5545,7 +5529,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5559,7 +5543,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5573,7 +5557,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5587,7 +5571,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5601,7 +5585,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5615,7 +5599,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5629,7 +5613,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5643,7 +5627,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5657,7 +5641,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5671,7 +5655,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5685,7 +5669,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5699,7 +5683,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5713,7 +5697,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5727,7 +5711,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5741,7 +5725,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5755,7 +5739,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5769,7 +5753,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5783,7 +5767,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5797,7 +5781,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5811,7 +5795,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5825,7 +5809,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5839,7 +5823,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5853,7 +5837,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5867,7 +5851,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5881,7 +5865,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5895,7 +5879,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5909,7 +5893,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5923,7 +5907,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5937,7 +5921,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5951,12 +5935,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -5970,7 +5954,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -5984,7 +5968,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -5998,7 +5982,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -6012,7 +5996,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -6026,7 +6010,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -6040,7 +6024,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -6054,7 +6038,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -6068,7 +6052,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -6082,7 +6066,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -6096,7 +6080,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -6110,7 +6094,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -6124,7 +6108,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -6138,7 +6122,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -6152,7 +6136,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -6166,7 +6150,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -6180,7 +6164,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -6194,7 +6178,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -6208,7 +6192,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -6222,7 +6206,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -6236,7 +6220,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -6250,7 +6234,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -6264,7 +6248,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -6278,7 +6262,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -6292,7 +6276,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -6306,7 +6290,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -6320,7 +6304,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -6334,7 +6318,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -6348,7 +6332,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -6362,7 +6346,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -6376,7 +6360,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -6390,7 +6374,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -6404,7 +6388,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -6418,7 +6402,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -6432,7 +6416,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -6446,7 +6430,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -6460,7 +6444,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -6474,7 +6458,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -6488,7 +6472,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -6502,7 +6486,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -6516,7 +6500,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -6530,7 +6514,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -6544,7 +6528,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -6558,7 +6542,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -6572,7 +6556,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -6586,7 +6570,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -6600,7 +6584,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -6614,7 +6598,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -6628,7 +6612,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -6642,7 +6626,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -6656,7 +6640,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -6670,7 +6654,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -6684,7 +6668,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -6698,7 +6682,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -6712,7 +6696,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -6726,7 +6710,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -6740,7 +6724,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -6754,7 +6738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -6768,7 +6752,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -6782,7 +6766,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -6796,7 +6780,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -6810,7 +6794,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -6824,7 +6808,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -6838,7 +6822,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -6852,7 +6836,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -6866,7 +6850,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -6880,7 +6864,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -6894,7 +6878,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -6908,7 +6892,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -6922,7 +6906,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -6936,7 +6920,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -6950,7 +6934,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -6964,7 +6948,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -6978,7 +6962,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -7015,29 +6999,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R131"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>250</v>
       </c>
@@ -7045,7 +7029,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -7053,7 +7037,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -7061,7 +7045,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -7069,13 +7053,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -7083,7 +7067,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -7098,7 +7082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -7112,7 +7096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -7126,7 +7110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -7140,7 +7124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -7154,7 +7138,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -7168,7 +7152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -7182,7 +7166,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -7196,7 +7180,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -7210,7 +7194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -7224,7 +7208,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -7238,7 +7222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7252,7 +7236,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7266,7 +7250,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7280,7 +7264,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7294,7 +7278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7308,7 +7292,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7322,7 +7306,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7336,7 +7320,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7350,7 +7334,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7364,7 +7348,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7378,7 +7362,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7392,7 +7376,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7406,7 +7390,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7420,7 +7404,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7434,7 +7418,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7448,7 +7432,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7462,7 +7446,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7476,7 +7460,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7490,7 +7474,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7504,7 +7488,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7518,7 +7502,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7532,7 +7516,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7546,7 +7530,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7560,7 +7544,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7574,7 +7558,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7588,7 +7572,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7602,7 +7586,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7616,7 +7600,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7630,7 +7614,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7644,7 +7628,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7658,7 +7642,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7672,7 +7656,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7686,7 +7670,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7700,7 +7684,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7714,7 +7698,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7728,7 +7712,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7742,7 +7726,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -7756,12 +7740,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -7775,7 +7759,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -7789,7 +7773,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -7803,7 +7787,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -7817,7 +7801,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -7831,7 +7815,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -7845,7 +7829,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -7859,7 +7843,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -7873,7 +7857,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -7887,7 +7871,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -7901,7 +7885,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -7915,7 +7899,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -7929,7 +7913,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -7943,7 +7927,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -7957,7 +7941,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -7971,7 +7955,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -7985,7 +7969,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -7999,7 +7983,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -8013,7 +7997,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -8027,7 +8011,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -8041,7 +8025,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -8055,7 +8039,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -8069,7 +8053,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -8083,7 +8067,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -8097,7 +8081,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -8111,7 +8095,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -8125,7 +8109,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -8139,7 +8123,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -8153,7 +8137,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -8167,7 +8151,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -8181,7 +8165,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -8195,7 +8179,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -8209,7 +8193,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -8223,7 +8207,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -8237,7 +8221,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -8251,7 +8235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -8265,7 +8249,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -8279,7 +8263,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -8293,7 +8277,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -8307,7 +8291,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -8321,7 +8305,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -8335,7 +8319,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -8349,7 +8333,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -8363,7 +8347,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -8377,7 +8361,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -8391,7 +8375,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -8405,7 +8389,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -8419,7 +8403,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -8433,7 +8417,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -8447,7 +8431,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -8461,7 +8445,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -8475,7 +8459,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -8489,7 +8473,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -8503,7 +8487,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -8517,7 +8501,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -8531,7 +8515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -8545,7 +8529,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -8559,7 +8543,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -8573,7 +8557,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -8587,7 +8571,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -8601,7 +8585,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -8615,7 +8599,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -8629,7 +8613,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -8643,7 +8627,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -8657,7 +8641,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -8671,7 +8655,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -8685,7 +8669,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -8699,7 +8683,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -8713,7 +8697,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -8727,7 +8711,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -8741,7 +8725,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -8755,7 +8739,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -8769,7 +8753,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -8783,7 +8767,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -8820,29 +8804,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>251</v>
       </c>
@@ -8850,7 +8834,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -8858,7 +8842,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -8866,7 +8850,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -8874,13 +8858,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -8888,7 +8872,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -8903,7 +8887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -8917,7 +8901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -8931,7 +8915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -8945,7 +8929,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -8959,7 +8943,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -8973,7 +8957,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -8987,7 +8971,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9001,7 +8985,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9015,7 +8999,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9029,7 +9013,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9043,7 +9027,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9057,7 +9041,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9071,7 +9055,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9085,7 +9069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9099,7 +9083,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9113,7 +9097,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9127,7 +9111,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9141,7 +9125,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9155,7 +9139,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9169,7 +9153,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9183,7 +9167,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9197,7 +9181,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9211,7 +9195,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9225,7 +9209,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9239,7 +9223,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9253,7 +9237,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9267,7 +9251,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9281,7 +9265,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9295,7 +9279,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9309,7 +9293,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9323,7 +9307,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9337,7 +9321,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9351,7 +9335,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9365,7 +9349,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9379,7 +9363,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9393,7 +9377,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9407,7 +9391,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9421,7 +9405,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9435,7 +9419,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9449,7 +9433,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9463,7 +9447,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9477,7 +9461,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9491,7 +9475,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9505,7 +9489,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9519,7 +9503,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9533,7 +9517,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9547,12 +9531,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -9566,7 +9550,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -9580,7 +9564,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -9594,7 +9578,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -9608,7 +9592,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -9622,7 +9606,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -9636,7 +9620,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -9650,7 +9634,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -9671,7 +9655,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -9692,7 +9676,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -9713,7 +9697,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -9734,7 +9718,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -9755,7 +9739,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -9776,7 +9760,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -9797,7 +9781,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -9818,7 +9802,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -9839,7 +9823,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -9860,7 +9844,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -9881,7 +9865,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -9902,7 +9886,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -9923,7 +9907,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -9944,7 +9928,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -9965,7 +9949,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -9986,7 +9970,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -10007,7 +9991,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -10028,7 +10012,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -10049,7 +10033,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -10070,7 +10054,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -10091,7 +10075,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -10112,7 +10096,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -10133,7 +10117,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -10154,7 +10138,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -10175,7 +10159,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -10196,7 +10180,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -10217,7 +10201,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -10238,7 +10222,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -10259,7 +10243,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -10280,7 +10264,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -10301,7 +10285,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -10322,7 +10306,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -10343,7 +10327,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -10364,7 +10348,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -10385,7 +10369,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -10406,7 +10390,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -10427,7 +10411,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -10448,7 +10432,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -10469,7 +10453,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -10490,7 +10474,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -10511,7 +10495,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -10532,7 +10516,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -10553,7 +10537,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -10574,7 +10558,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -10595,7 +10579,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -10616,7 +10600,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -10637,7 +10621,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -10658,7 +10642,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -10679,7 +10663,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -10700,7 +10684,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -10721,7 +10705,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -10742,7 +10726,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -10763,7 +10747,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -10784,7 +10768,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -10805,7 +10789,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -10826,7 +10810,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -10847,7 +10831,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -10868,7 +10852,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -10889,7 +10873,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -10910,7 +10894,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -10931,7 +10915,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -10952,7 +10936,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -10973,7 +10957,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -10994,7 +10978,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -11015,7 +10999,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -11036,7 +11020,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -11057,7 +11041,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -11078,7 +11062,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -11122,29 +11106,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>252</v>
       </c>
@@ -11152,7 +11136,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -11160,7 +11144,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -11168,7 +11152,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -11176,13 +11160,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -11190,7 +11174,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -11205,7 +11189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11219,7 +11203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11233,7 +11217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11247,7 +11231,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11261,7 +11245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11275,7 +11259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11289,7 +11273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11303,7 +11287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11317,7 +11301,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11331,7 +11315,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11345,7 +11329,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11359,7 +11343,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11373,7 +11357,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11387,7 +11371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11401,7 +11385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11415,7 +11399,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11429,7 +11413,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11443,7 +11427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11457,7 +11441,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11471,7 +11455,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11485,7 +11469,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11499,7 +11483,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11513,7 +11497,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11527,7 +11511,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11541,7 +11525,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11555,7 +11539,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11569,7 +11553,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11583,7 +11567,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11597,7 +11581,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11611,7 +11595,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -11625,7 +11609,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -11639,7 +11623,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -11653,7 +11637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -11667,7 +11651,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -11681,7 +11665,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -11695,7 +11679,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -11709,7 +11693,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -11723,7 +11707,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -11737,7 +11721,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -11751,7 +11735,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -11765,7 +11749,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -11779,7 +11763,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -11793,7 +11777,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -11807,7 +11791,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -11821,7 +11805,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -11835,7 +11819,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -11849,12 +11833,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -11868,7 +11852,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -11882,7 +11866,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -11896,7 +11880,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -11910,7 +11894,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -11924,7 +11908,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -11938,7 +11922,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -11952,7 +11936,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -11973,7 +11957,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -11994,7 +11978,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -12015,7 +11999,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -12036,7 +12020,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -12057,7 +12041,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -12078,7 +12062,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -12099,7 +12083,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -12120,7 +12104,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -12141,7 +12125,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -12162,7 +12146,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -12183,7 +12167,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -12204,7 +12188,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -12225,7 +12209,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -12246,7 +12230,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -12267,7 +12251,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -12288,7 +12272,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -12309,7 +12293,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -12330,7 +12314,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -12351,7 +12335,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -12372,7 +12356,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -12393,7 +12377,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -12414,7 +12398,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -12435,7 +12419,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -12456,7 +12440,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -12477,7 +12461,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -12498,7 +12482,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -12519,7 +12503,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -12540,7 +12524,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -12561,7 +12545,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -12582,7 +12566,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -12603,7 +12587,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -12624,7 +12608,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -12645,7 +12629,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -12666,7 +12650,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -12687,7 +12671,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -12708,7 +12692,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -12729,7 +12713,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -12750,7 +12734,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -12771,7 +12755,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -12792,7 +12776,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -12813,7 +12797,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -12834,7 +12818,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -12855,7 +12839,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -12876,7 +12860,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -12897,7 +12881,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -12918,7 +12902,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -12939,7 +12923,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -12960,7 +12944,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -12981,7 +12965,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -13002,7 +12986,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -13023,7 +13007,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -13044,7 +13028,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -13065,7 +13049,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -13086,7 +13070,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -13107,7 +13091,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -13128,7 +13112,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -13149,7 +13133,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -13170,7 +13154,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -13191,7 +13175,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -13212,7 +13196,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -13233,7 +13217,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -13254,7 +13238,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -13275,7 +13259,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -13296,7 +13280,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -13317,7 +13301,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -13338,7 +13322,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -13359,7 +13343,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -13380,7 +13364,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -13424,29 +13408,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>253</v>
       </c>
@@ -13454,7 +13438,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -13462,7 +13446,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -13470,7 +13454,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -13478,13 +13462,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -13492,7 +13476,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -13507,7 +13491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -13521,7 +13505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -13535,7 +13519,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -13549,7 +13533,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -13563,7 +13547,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -13577,7 +13561,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -13591,7 +13575,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -13605,7 +13589,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -13619,7 +13603,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -13633,7 +13617,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -13647,7 +13631,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -13661,7 +13645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -13675,7 +13659,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -13689,7 +13673,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -13703,7 +13687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -13717,7 +13701,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -13731,7 +13715,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -13745,7 +13729,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -13759,7 +13743,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -13773,7 +13757,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -13787,7 +13771,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -13801,7 +13785,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -13815,7 +13799,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -13829,7 +13813,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -13843,7 +13827,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -13857,7 +13841,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -13871,7 +13855,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -13885,7 +13869,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -13899,7 +13883,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -13913,7 +13897,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -13927,7 +13911,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -13941,7 +13925,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -13955,7 +13939,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -13969,7 +13953,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -13983,7 +13967,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -13997,7 +13981,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14011,7 +13995,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14025,7 +14009,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14039,7 +14023,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14053,7 +14037,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14067,7 +14051,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14081,7 +14065,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14095,7 +14079,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14109,7 +14093,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14123,7 +14107,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14137,7 +14121,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14151,12 +14135,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -14170,7 +14154,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -14184,7 +14168,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -14198,7 +14182,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -14212,7 +14196,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -14226,7 +14210,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -14240,7 +14224,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -14254,7 +14238,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -14275,7 +14259,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -14296,7 +14280,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -14317,7 +14301,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -14338,7 +14322,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -14359,7 +14343,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -14380,7 +14364,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -14401,7 +14385,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -14422,7 +14406,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -14443,7 +14427,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -14464,7 +14448,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -14485,7 +14469,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -14506,7 +14490,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -14527,7 +14511,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -14548,7 +14532,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -14569,7 +14553,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -14590,7 +14574,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -14611,7 +14595,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -14632,7 +14616,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -14653,7 +14637,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -14674,7 +14658,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -14695,7 +14679,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -14716,7 +14700,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -14737,7 +14721,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -14758,7 +14742,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -14779,7 +14763,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -14800,7 +14784,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -14821,7 +14805,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -14842,7 +14826,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -14863,7 +14847,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -14884,7 +14868,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -14905,7 +14889,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -14926,7 +14910,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -14947,7 +14931,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -14968,7 +14952,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -14989,7 +14973,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -15010,7 +14994,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -15031,7 +15015,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -15052,7 +15036,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -15073,7 +15057,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -15094,7 +15078,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -15115,7 +15099,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -15136,7 +15120,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -15157,7 +15141,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -15178,7 +15162,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -15199,7 +15183,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -15220,7 +15204,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -15241,7 +15225,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -15262,7 +15246,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -15283,7 +15267,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -15304,7 +15288,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -15325,7 +15309,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -15346,7 +15330,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -15367,7 +15351,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -15388,7 +15372,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -15409,7 +15393,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -15430,7 +15414,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -15451,7 +15435,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -15472,7 +15456,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -15493,7 +15477,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -15514,7 +15498,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -15535,7 +15519,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -15556,7 +15540,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -15577,7 +15561,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -15598,7 +15582,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -15619,7 +15603,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -15640,7 +15624,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -15661,7 +15645,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -15682,7 +15666,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -15726,29 +15710,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>254</v>
       </c>
@@ -15756,7 +15740,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -15764,7 +15748,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -15772,7 +15756,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -15780,13 +15764,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -15794,7 +15778,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -15809,7 +15793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -15823,7 +15807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -15837,7 +15821,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -15851,7 +15835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -15865,7 +15849,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -15879,7 +15863,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -15893,7 +15877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -15907,7 +15891,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -15921,7 +15905,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -15935,7 +15919,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -15949,7 +15933,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -15963,7 +15947,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -15977,7 +15961,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -15991,7 +15975,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16005,7 +15989,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16019,7 +16003,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16033,7 +16017,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16047,7 +16031,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16061,7 +16045,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16075,7 +16059,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16089,7 +16073,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16103,7 +16087,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16117,7 +16101,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16131,7 +16115,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16145,7 +16129,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16159,7 +16143,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16173,7 +16157,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16187,7 +16171,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16201,7 +16185,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16215,7 +16199,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16229,7 +16213,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16243,7 +16227,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16257,7 +16241,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16271,7 +16255,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16285,7 +16269,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16299,7 +16283,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16313,7 +16297,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16327,7 +16311,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16341,7 +16325,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16355,7 +16339,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16369,7 +16353,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16383,7 +16367,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16397,7 +16381,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16411,7 +16395,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -16425,7 +16409,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -16439,7 +16423,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -16453,12 +16437,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -16472,7 +16456,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -16486,7 +16470,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -16500,7 +16484,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -16514,7 +16498,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -16528,7 +16512,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -16542,7 +16526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -16556,7 +16540,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -16577,7 +16561,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -16598,7 +16582,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -16619,7 +16603,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -16640,7 +16624,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -16661,7 +16645,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -16682,7 +16666,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -16703,7 +16687,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -16724,7 +16708,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -16745,7 +16729,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -16766,7 +16750,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -16787,7 +16771,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -16808,7 +16792,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -16829,7 +16813,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -16850,7 +16834,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -16871,7 +16855,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -16892,7 +16876,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -16913,7 +16897,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -16934,7 +16918,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -16955,7 +16939,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -16976,7 +16960,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -16997,7 +16981,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -17018,7 +17002,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -17039,7 +17023,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -17060,7 +17044,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -17081,7 +17065,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -17102,7 +17086,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -17123,7 +17107,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -17144,7 +17128,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -17165,7 +17149,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -17186,7 +17170,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -17207,7 +17191,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -17228,7 +17212,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -17249,7 +17233,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -17270,7 +17254,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -17291,7 +17275,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -17312,7 +17296,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -17333,7 +17317,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -17354,7 +17338,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -17375,7 +17359,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -17396,7 +17380,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -17417,7 +17401,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -17438,7 +17422,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -17459,7 +17443,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -17480,7 +17464,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -17501,7 +17485,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -17522,7 +17506,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -17543,7 +17527,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -17564,7 +17548,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -17585,7 +17569,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -17606,7 +17590,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -17627,7 +17611,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -17648,7 +17632,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -17669,7 +17653,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -17690,7 +17674,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -17711,7 +17695,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -17732,7 +17716,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -17753,7 +17737,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -17774,7 +17758,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -17795,7 +17779,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -17816,7 +17800,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -17837,7 +17821,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -17858,7 +17842,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -17879,7 +17863,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -17900,7 +17884,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -17921,7 +17905,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -17942,7 +17926,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -17963,7 +17947,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -17984,7 +17968,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -18028,29 +18012,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>255</v>
       </c>
@@ -18058,7 +18042,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -18066,7 +18050,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -18074,7 +18058,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -18082,13 +18066,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -18096,7 +18080,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -18111,7 +18095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -18125,7 +18109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -18139,7 +18123,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -18153,7 +18137,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -18167,7 +18151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -18181,7 +18165,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -18195,7 +18179,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -18209,7 +18193,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -18223,7 +18207,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -18237,7 +18221,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -18251,7 +18235,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -18265,7 +18249,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -18279,7 +18263,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -18293,7 +18277,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -18307,7 +18291,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -18321,7 +18305,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -18335,7 +18319,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -18349,7 +18333,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -18363,7 +18347,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -18377,7 +18361,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -18391,7 +18375,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -18405,7 +18389,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -18419,7 +18403,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -18433,7 +18417,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -18447,7 +18431,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -18461,7 +18445,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -18475,7 +18459,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -18489,7 +18473,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -18503,7 +18487,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -18517,7 +18501,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -18531,7 +18515,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -18545,7 +18529,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -18559,7 +18543,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -18573,7 +18557,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -18587,7 +18571,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -18601,7 +18585,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -18615,7 +18599,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -18629,7 +18613,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -18643,7 +18627,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -18657,7 +18641,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -18671,7 +18655,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -18685,7 +18669,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -18699,7 +18683,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -18713,7 +18697,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -18727,7 +18711,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -18741,7 +18725,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -18755,12 +18739,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -18774,7 +18758,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -18788,7 +18772,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -18802,7 +18786,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -18816,7 +18800,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -18830,7 +18814,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -18844,7 +18828,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -18858,7 +18842,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -18879,7 +18863,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -18900,7 +18884,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -18921,7 +18905,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -18942,7 +18926,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -18963,7 +18947,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -18984,7 +18968,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -19005,7 +18989,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -19026,7 +19010,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -19047,7 +19031,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -19068,7 +19052,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -19089,7 +19073,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -19110,7 +19094,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -19131,7 +19115,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -19152,7 +19136,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -19173,7 +19157,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -19194,7 +19178,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -19215,7 +19199,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -19236,7 +19220,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -19257,7 +19241,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -19278,7 +19262,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -19299,7 +19283,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -19320,7 +19304,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -19341,7 +19325,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -19362,7 +19346,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -19383,7 +19367,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -19404,7 +19388,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -19425,7 +19409,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -19446,7 +19430,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -19467,7 +19451,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -19488,7 +19472,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -19509,7 +19493,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -19530,7 +19514,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -19551,7 +19535,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -19572,7 +19556,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -19593,7 +19577,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -19614,7 +19598,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -19635,7 +19619,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -19656,7 +19640,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -19677,7 +19661,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -19698,7 +19682,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -19719,7 +19703,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -19740,7 +19724,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -19761,7 +19745,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -19782,7 +19766,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -19803,7 +19787,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -19824,7 +19808,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -19845,7 +19829,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -19866,7 +19850,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -19887,7 +19871,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -19908,7 +19892,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -19929,7 +19913,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -19950,7 +19934,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -19971,7 +19955,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -19992,7 +19976,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -20013,7 +19997,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -20034,7 +20018,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -20055,7 +20039,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -20076,7 +20060,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -20097,7 +20081,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -20118,7 +20102,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -20139,7 +20123,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -20160,7 +20144,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -20181,7 +20165,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -20202,7 +20186,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -20223,7 +20207,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -20244,7 +20228,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -20265,7 +20249,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -20286,7 +20270,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
